--- a/testcase/环境感知联动功能测试用例.xlsx
+++ b/testcase/环境感知联动功能测试用例.xlsx
@@ -909,7 +909,7 @@
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>打开说明弹窗；说明人体、门窗、温湿度感知，以及生效范围、最多16个动作、相邻动作限制、末尾延时限制和解除锁定规则。</t>
+          <t>打开说明弹窗；说明人体、门窗、温湿度感知，以及生效范围、最多16个动作、相邻动作限制、末尾延时限制、延时动作5-240分钟且用于避免频繁控制、解除锁定等规则。</t>
         </is>
       </c>
       <c r="L7" s="5" t="inlineStr">
@@ -7284,7 +7284,7 @@
       </c>
       <c r="E107" s="6" t="inlineStr">
         <is>
-          <t>延时动作 1 分钟</t>
+          <t>延时动作 5 分钟</t>
         </is>
       </c>
       <c r="F107" s="5" t="inlineStr">
@@ -7304,7 +7304,7 @@
       </c>
       <c r="I107" s="6" t="inlineStr">
         <is>
-          <t>延时=1</t>
+          <t>延时=5</t>
         </is>
       </c>
       <c r="J107" s="6" t="inlineStr">
@@ -7414,7 +7414,7 @@
       </c>
       <c r="E109" s="6" t="inlineStr">
         <is>
-          <t>延时动作 0 分钟</t>
+          <t>延时动作 4 分钟</t>
         </is>
       </c>
       <c r="F109" s="5" t="inlineStr">
@@ -7434,7 +7434,7 @@
       </c>
       <c r="I109" s="6" t="inlineStr">
         <is>
-          <t>延时=0</t>
+          <t>延时=4</t>
         </is>
       </c>
       <c r="J109" s="6" t="inlineStr">
@@ -7446,7 +7446,7 @@
       </c>
       <c r="K109" s="6" t="inlineStr">
         <is>
-          <t>提示“延时时长请输入 1-240 分钟的整数”。</t>
+          <t>提示“延时时长请输入 5-240 分钟的整数”。</t>
         </is>
       </c>
       <c r="L109" s="5" t="inlineStr">
@@ -7511,7 +7511,7 @@
       </c>
       <c r="K110" s="8" t="inlineStr">
         <is>
-          <t>提示“延时时长请输入 1-240 分钟的整数”。</t>
+          <t>提示“延时时长请输入 5-240 分钟的整数”。</t>
         </is>
       </c>
       <c r="L110" s="7" t="inlineStr">
@@ -7576,7 +7576,7 @@
       </c>
       <c r="K111" s="6" t="inlineStr">
         <is>
-          <t>提示“延时时长请输入 1-240 分钟的整数”。</t>
+          <t>提示“延时时长请输入 5-240 分钟的整数”。</t>
         </is>
       </c>
       <c r="L111" s="5" t="inlineStr">
@@ -7641,7 +7641,7 @@
       </c>
       <c r="K112" s="8" t="inlineStr">
         <is>
-          <t>提示“延时时长请输入 1-240 分钟的整数”。</t>
+          <t>提示“延时时长请输入 5-240 分钟的整数”。</t>
         </is>
       </c>
       <c r="L112" s="7" t="inlineStr">
@@ -10933,7 +10933,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
@@ -11030,8 +11029,6 @@
       <c r="E8" s="12" t="n"/>
       <c r="F8" s="13" t="n"/>
     </row>
-    <row r="9"/>
-    <row r="10"/>
     <row r="11">
       <c r="A11" s="11" t="inlineStr">
         <is>
@@ -11189,7 +11186,7 @@
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>空调参数、延时、动作顺序、相邻限制和16个上限</t>
+          <t>空调参数、延时5~240分钟边界、动作顺序、相邻限制和16个上限</t>
         </is>
       </c>
       <c r="D19" s="12" t="n"/>
@@ -11268,7 +11265,6 @@
       <c r="E23" s="12" t="n"/>
       <c r="F23" s="13" t="n"/>
     </row>
-    <row r="24"/>
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
@@ -11277,7 +11273,7 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>温度触发 -10~50℃；湿度 1~99%；持续 1~60分钟；延时 1~240分钟；空调温度 16~30℃；锁定温度 16~30℃；执行动作最多16个。</t>
+          <t>温度触发 -10~50℃；湿度 1~99%；持续 1~60分钟；延时 5~240分钟；空调温度 16~30℃；锁定温度 16~30℃；执行动作最多16个。</t>
         </is>
       </c>
       <c r="C25" s="12" t="n"/>

--- a/testcase/环境感知联动功能测试用例.xlsx
+++ b/testcase/环境感知联动功能测试用例.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="测试用例" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖说明" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="测试用例" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="覆盖说明" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'测试用例'!$A$4:$O$161</definedName>
@@ -835,7 +835,7 @@
       </c>
       <c r="I6" s="8" t="inlineStr">
         <is>
-          <t>默认3条任务</t>
+          <t>默认10条任务</t>
         </is>
       </c>
       <c r="J6" s="8" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="K6" s="8" t="inlineStr">
         <is>
-          <t>显示3条默认任务；列包含任务名称、生效日期、生效时间、控制策略、最后修改时间、任务状态、操作。</t>
+          <t>显示10条默认任务；列包含任务名称、生效日期、生效时间、控制策略、最后修改时间、任务状态、操作。</t>
         </is>
       </c>
       <c r="L6" s="7" t="inlineStr">
@@ -9297,7 +9297,7 @@
       </c>
       <c r="K138" s="8" t="inlineStr">
         <is>
-          <t>弹窗标题包含任务名称；显示满足组合条件、持续复核通过和复核未通过记录；结果包含成功和跳过。</t>
+          <t>弹窗标题包含任务名称；日志不罗列组合条件内容，条件状态只有“满足组合条件/持续满足组合条件/未持续满足组合条件”三种，后接执行动作内容（动作类型为空调控制/空调锁定/延时，动作链首个动作带条件状态前缀，如“满足组合条件，执行空调控制：开机 / 制冷 / 26℃ / 中风。”“执行空调锁定：锁定开机 / 模式锁定制冷 / 温度锁定16-30℃。”“执行延时：10 分钟。”）；执行结果含“成功/异常/跳过”三种状态标签；异常记录文本为“满足组合条件，执行空调控制：开机 / 制冷 / 26℃ / 中风，部分空调（1-2-1-2）由于【设备离线】未执行成功。”，【】内失败原因按实际情况填写（示例含设备离线、状态锁定两种）；配置持续满足条件的任务另显示“未持续满足组合条件，本次不执行动作。”（跳过）。</t>
         </is>
       </c>
       <c r="L138" s="7" t="inlineStr">

--- a/testcase/环境感知联动功能测试用例.xlsx
+++ b/testcase/环境感知联动功能测试用例.xlsx
@@ -402,7 +402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O172"/>
+  <dimension ref="A1:O176"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -595,7 +595,7 @@
         <v>1. 点击弹窗标题旁“?”</v>
       </c>
       <c r="K7" t="str">
-        <v>打开说明弹窗；说明人体、门窗、温湿度感知，以及生效范围、最多16个动作、相邻动作限制、末尾延时限制、延时动作5-240分钟且用于避免频繁控制、解除锁定等规则。</v>
+        <v>打开说明弹窗；说明人体、门窗、温湿度感知，以及生效范围、最多16个动作、相邻动作限制、控制类动作（空调控制/锁定控制）后必须紧跟延时（最后一个动作除外）、末尾延时限制、延时动作5-240分钟且用于避免频繁控制、解除锁定等规则。</v>
       </c>
       <c r="L7" t="str">
         <v>待测试</v>
@@ -5914,7 +5914,7 @@
         <v>开关机锁定</v>
       </c>
       <c r="E118" t="str">
-        <v>锁定开机和锁定关机</v>
+        <v>禁止关机和禁止启动</v>
       </c>
       <c r="F118" t="str">
         <v>P0</v>
@@ -5926,7 +5926,7 @@
         <v>打开集控计费平台并登录项目账号（须开启环境感知监测偏好设置），进入“节能策略 &gt; 环境感知联动”页面。点击“新建任务”，进入新建任务弹窗。</v>
       </c>
       <c r="I118" t="str">
-        <v>分别选择锁定开机、锁定关机</v>
+        <v>分别选择禁止关机、禁止启动</v>
       </c>
       <c r="J118" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 分别配置锁定值_x000d_
@@ -6887,7 +6887,7 @@
         <v>1. 点击“日志”</v>
       </c>
       <c r="K138" t="str">
-        <v>弹窗标题包含任务名称；日志不罗列组合条件内容，条件状态只有“满足组合条件/持续满足组合条件/未持续满足组合条件”三种，后接执行动作内容（动作类型为空调控制/空调锁定/延时，动作链首个动作带条件状态前缀，如“满足组合条件，执行空调控制：开机 / 制冷 / 26℃ / 中风。”“执行空调锁定：锁定开机 / 模式锁定制冷 / 温度锁定16-30℃。”“执行延时：10 分钟。”）；执行结果含“成功/异常/跳过”三种状态标签；异常记录文本为“满足组合条件，执行空调控制：开机 / 制冷 / 26℃ / 中风，部分空调（1-2-1-2）由于【设备离线】未执行成功。”，【】内失败原因按实际情况填写（示例含设备离线、状态锁定两种）；配置持续满足条件的任务另显示“未持续满足组合条件，本次不执行动作。”（跳过）。</v>
+        <v>弹窗标题包含任务名称；日志不罗列组合条件内容，条件状态只有“满足组合条件/持续满足组合条件/未持续满足组合条件”三种，后接执行动作内容（动作类型为空调控制/空调锁定/延时，动作链首个动作带条件状态前缀，如“满足组合条件，执行空调控制：开机 / 制冷 / 26℃ / 中风。”“执行空调锁定：禁止关机 / 模式锁定制冷 / 温度锁定16-30℃。”“执行延时：10 分钟。”）；执行结果含“成功/异常/跳过”三种状态标签；异常记录文本为“满足组合条件，执行空调控制：开机 / 制冷 / 26℃ / 中风，部分空调（1-2-1-2）由于【设备离线】未执行成功。”，【】内失败原因按实际情况填写（示例含设备离线、状态锁定两种）；配置持续满足条件的任务另显示“未持续满足组合条件，本次不执行动作。”（跳过）。</v>
       </c>
       <c r="L138" t="str">
         <v>待测试</v>
@@ -8561,6 +8561,201 @@
         <v/>
       </c>
       <c r="O172" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="173" xml:space="preserve">
+      <c r="A173">
+        <v>169</v>
+      </c>
+      <c r="B173" t="str">
+        <v>ENV-169</v>
+      </c>
+      <c r="C173" t="str">
+        <v>执行动作</v>
+      </c>
+      <c r="D173" t="str">
+        <v>动作序列</v>
+      </c>
+      <c r="E173" t="str">
+        <v>空调控制后直接接锁定控制禁止保存</v>
+      </c>
+      <c r="F173" t="str">
+        <v>P0</v>
+      </c>
+      <c r="G173" t="str">
+        <v>异常</v>
+      </c>
+      <c r="H173" t="str">
+        <v>打开集控计费平台并登录项目账号（须开启环境感知监测偏好设置），进入“节能策略 &gt; 环境感知联动”页面。点击“新建任务”，进入新建任务弹窗。</v>
+      </c>
+      <c r="I173" t="str">
+        <v>空调控制→锁定控制</v>
+      </c>
+      <c r="J173" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. 配置空调控制动作后直接添加锁定控制动作（中间无延时）_x000d_
+2. 输入各自有效参数_x000d_
+3. 保存</v>
+      </c>
+      <c r="K173" t="str">
+        <v>提示“空调控制或锁定控制后必须紧跟一个延时动作”。</v>
+      </c>
+      <c r="L173" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M173" t="str">
+        <v/>
+      </c>
+      <c r="N173" t="str">
+        <v/>
+      </c>
+      <c r="O173" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="174" xml:space="preserve">
+      <c r="A174">
+        <v>170</v>
+      </c>
+      <c r="B174" t="str">
+        <v>ENV-170</v>
+      </c>
+      <c r="C174" t="str">
+        <v>执行动作</v>
+      </c>
+      <c r="D174" t="str">
+        <v>动作序列</v>
+      </c>
+      <c r="E174" t="str">
+        <v>锁定控制后直接接空调控制禁止保存</v>
+      </c>
+      <c r="F174" t="str">
+        <v>P0</v>
+      </c>
+      <c r="G174" t="str">
+        <v>异常</v>
+      </c>
+      <c r="H174" t="str">
+        <v>打开集控计费平台并登录项目账号（须开启环境感知监测偏好设置），进入“节能策略 &gt; 环境感知联动”页面。点击“新建任务”，进入新建任务弹窗。</v>
+      </c>
+      <c r="I174" t="str">
+        <v>锁定控制→空调控制</v>
+      </c>
+      <c r="J174" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. 配置锁定控制动作后直接添加空调控制动作（中间无延时）_x000d_
+2. 输入各自有效参数_x000d_
+3. 保存</v>
+      </c>
+      <c r="K174" t="str">
+        <v>提示“空调控制或锁定控制后必须紧跟一个延时动作”。</v>
+      </c>
+      <c r="L174" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M174" t="str">
+        <v/>
+      </c>
+      <c r="N174" t="str">
+        <v/>
+      </c>
+      <c r="O174" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="175" xml:space="preserve">
+      <c r="A175">
+        <v>171</v>
+      </c>
+      <c r="B175" t="str">
+        <v>ENV-171</v>
+      </c>
+      <c r="C175" t="str">
+        <v>执行动作</v>
+      </c>
+      <c r="D175" t="str">
+        <v>动作序列</v>
+      </c>
+      <c r="E175" t="str">
+        <v>控制类动作位于末位时无需跟延时</v>
+      </c>
+      <c r="F175" t="str">
+        <v>P1</v>
+      </c>
+      <c r="G175" t="str">
+        <v>功能</v>
+      </c>
+      <c r="H175" t="str">
+        <v>打开集控计费平台并登录项目账号（须开启环境感知监测偏好设置），进入“节能策略 &gt; 环境感知联动”页面。点击“新建任务”，进入新建任务弹窗。</v>
+      </c>
+      <c r="I175" t="str">
+        <v>延时→锁定控制（末位）</v>
+      </c>
+      <c r="J175" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. 配置延时动作后接锁定控制动作，锁定控制为最后一个动作_x000d_
+2. 输入有效参数_x000d_
+3. 保存</v>
+      </c>
+      <c r="K175" t="str">
+        <v>允许保存；摘要按配置顺序显示动作链。</v>
+      </c>
+      <c r="L175" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M175" t="str">
+        <v/>
+      </c>
+      <c r="N175" t="str">
+        <v/>
+      </c>
+      <c r="O175" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="176" xml:space="preserve">
+      <c r="A176">
+        <v>172</v>
+      </c>
+      <c r="B176" t="str">
+        <v>ENV-172</v>
+      </c>
+      <c r="C176" t="str">
+        <v>执行动作</v>
+      </c>
+      <c r="D176" t="str">
+        <v>动作序列</v>
+      </c>
+      <c r="E176" t="str">
+        <v>锁定控制后添加动作默认为延时</v>
+      </c>
+      <c r="F176" t="str">
+        <v>P1</v>
+      </c>
+      <c r="G176" t="str">
+        <v>功能</v>
+      </c>
+      <c r="H176" t="str">
+        <v>打开集控计费平台并登录项目账号（须开启环境感知监测偏好设置），进入“节能策略 &gt; 环境感知联动”页面。点击“新建任务”，进入新建任务弹窗。</v>
+      </c>
+      <c r="I176" t="str">
+        <v>上一动作为锁定控制</v>
+      </c>
+      <c r="J176" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. 配置一个锁定控制动作_x000d_
+2. 点击“添加动作”</v>
+      </c>
+      <c r="K176" t="str">
+        <v>新增动作默认类型为延时（默认 10 分钟）。</v>
+      </c>
+      <c r="L176" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M176" t="str">
+        <v/>
+      </c>
+      <c r="N176" t="str">
+        <v/>
+      </c>
+      <c r="O176" t="str">
         <v/>
       </c>
     </row>
@@ -8573,7 +8768,7 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O172"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O176"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -8608,15 +8803,15 @@
         <v>近期核心提交</v>
       </c>
       <c r="B5" t="str">
-        <v>efb75df 环境感知联动四期修改；cce7a94 增加删除、停用任务时的提示</v>
+        <v>efb75df 环境感知联动四期修改；cce7a94 增加删除、停用任务时的提示；2026-09-09 动作链控制类动作后须紧跟延时、开关机锁定选项更名禁止关机/禁止启动</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
         <v>用例总数</v>
       </c>
-      <c r="B6" t="str">
-        <v>168</v>
+      <c r="B6">
+        <v>172</v>
       </c>
     </row>
     <row r="7">
@@ -8728,10 +8923,10 @@
         <v>执行动作</v>
       </c>
       <c r="B19">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C19" t="str">
-        <v>空调参数、延时5~240分钟边界、动作顺序、相邻限制和16个上限</v>
+        <v>空调参数、延时5~240分钟边界、动作顺序、相邻限制、控制类动作后须紧跟延时和16个上限</v>
       </c>
     </row>
     <row r="20">
@@ -8802,7 +8997,7 @@
         <v>关键规则</v>
       </c>
       <c r="B27" t="str">
-        <v>最多4类且不重复的触发条件；至少1个条件和1个动作；相邻动作类型不得相同；最后一个动作不得为延时；制热不得与制冷或除湿同时锁定。生效日期和生效时间仅控制动作链启动，不中断已启动动作；停用或删除仍立即终止执行实例。人在状态/门窗状态/湿度条件要求所选每个房间均绑定对应传感器,任一房间未绑定则阻止保存并提示;温度条件不做绑定校验,房间无温湿度传感器时使用空调回风温度判定。</v>
+        <v>最多4类且不重复的触发条件；至少1个条件和1个动作；相邻动作类型不得相同；控制类动作（空调控制/锁定控制）后必须紧跟一个延时（最后一个动作除外）；最后一个动作不得为延时；制热不得与制冷或除湿同时锁定。生效日期和生效时间仅控制动作链启动，不中断已启动动作；停用或删除仍立即终止执行实例。人在状态/门窗状态/湿度条件要求所选每个房间均绑定对应传感器,任一房间未绑定则阻止保存并提示;温度条件不做绑定校验,房间无温湿度传感器时使用空调回风温度判定。</v>
       </c>
     </row>
   </sheetData>

--- a/testcase/环境感知联动功能测试用例.xlsx
+++ b/testcase/环境感知联动功能测试用例.xlsx
@@ -402,7 +402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O176"/>
+  <dimension ref="A1:O179"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -8756,6 +8756,152 @@
         <v/>
       </c>
       <c r="O176" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="177" xml:space="preserve">
+      <c r="A177">
+        <v>173</v>
+      </c>
+      <c r="B177" t="str">
+        <v>ENV-173</v>
+      </c>
+      <c r="C177" t="str">
+        <v>任务生命周期</v>
+      </c>
+      <c r="D177" t="str">
+        <v>日志</v>
+      </c>
+      <c r="E177" t="str">
+        <v>创建任务写入日志</v>
+      </c>
+      <c r="F177" t="str">
+        <v>P1</v>
+      </c>
+      <c r="G177" t="str">
+        <v>功能</v>
+      </c>
+      <c r="H177" t="str">
+        <v>打开集控计费平台并登录项目账号（须开启环境感知监测偏好设置），进入“节能策略 &gt; 环境感知联动”页面。点击“新建任务”，进入新建任务弹窗。</v>
+      </c>
+      <c r="I177" t="str">
+        <v>正常填写并保存一个新任务</v>
+      </c>
+      <c r="J177" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. 新建任务并保存_x000d_
+2. 在该任务操作列点击“日志”</v>
+      </c>
+      <c r="K177" t="str">
+        <v>日志中显示“创建任务”记录，时间为任务创建时间；该记录不带条件状态前缀，执行结果列留空。</v>
+      </c>
+      <c r="L177" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M177" t="str">
+        <v/>
+      </c>
+      <c r="N177" t="str">
+        <v/>
+      </c>
+      <c r="O177" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="178" xml:space="preserve">
+      <c r="A178">
+        <v>174</v>
+      </c>
+      <c r="B178" t="str">
+        <v>ENV-174</v>
+      </c>
+      <c r="C178" t="str">
+        <v>任务生命周期</v>
+      </c>
+      <c r="D178" t="str">
+        <v>日志</v>
+      </c>
+      <c r="E178" t="str">
+        <v>编辑任务内容记录实际变更维度</v>
+      </c>
+      <c r="F178" t="str">
+        <v>P0</v>
+      </c>
+      <c r="G178" t="str">
+        <v>功能</v>
+      </c>
+      <c r="H178" t="str">
+        <v>打开集控计费平台并登录项目账号（须开启环境感知监测偏好设置），进入“节能策略 &gt; 环境感知联动”页面。存在一个停用状态的任务。</v>
+      </c>
+      <c r="I178" t="str">
+        <v>修改任务的生效日期与执行动作，其余配置不变</v>
+      </c>
+      <c r="J178" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. 停用任务后点击“编辑”_x000d_
+2. 修改生效日期与执行动作_x000d_
+3. 保存后打开日志</v>
+      </c>
+      <c r="K178" t="str">
+        <v>日志中新增“编辑任务内容（生效日期、执行动作）”记录；括号内仅列出实际发生变更的配置维度，以“、”连接；不带条件状态前缀，执行结果列留空。</v>
+      </c>
+      <c r="L178" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M178" t="str">
+        <v/>
+      </c>
+      <c r="N178" t="str">
+        <v/>
+      </c>
+      <c r="O178" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="179" xml:space="preserve">
+      <c r="A179">
+        <v>175</v>
+      </c>
+      <c r="B179" t="str">
+        <v>ENV-175</v>
+      </c>
+      <c r="C179" t="str">
+        <v>任务生命周期</v>
+      </c>
+      <c r="D179" t="str">
+        <v>日志</v>
+      </c>
+      <c r="E179" t="str">
+        <v>启用停用写入日志并按时间倒序展示</v>
+      </c>
+      <c r="F179" t="str">
+        <v>P0</v>
+      </c>
+      <c r="G179" t="str">
+        <v>功能</v>
+      </c>
+      <c r="H179" t="str">
+        <v>打开集控计费平台并登录项目账号（须开启环境感知监测偏好设置），进入“节能策略 &gt; 环境感知联动”页面。存在一个已产生动作执行记录的任务。</v>
+      </c>
+      <c r="I179" t="str">
+        <v>对该任务先停用再启用</v>
+      </c>
+      <c r="J179" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. 停用任务_x000d_
+2. 再次启用任务_x000d_
+3. 打开日志</v>
+      </c>
+      <c r="K179" t="str">
+        <v>日志中依次出现“停用任务”“启用任务”记录；状态变动记录与动作执行记录在同一日志流中按时间倒序排列，同一执行实例的多个动作按实际执行时间正序连续展示。</v>
+      </c>
+      <c r="L179" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M179" t="str">
+        <v/>
+      </c>
+      <c r="N179" t="str">
+        <v/>
+      </c>
+      <c r="O179" t="str">
         <v/>
       </c>
     </row>
@@ -8768,7 +8914,7 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O176"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O179"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -8803,7 +8949,7 @@
         <v>近期核心提交</v>
       </c>
       <c r="B5" t="str">
-        <v>efb75df 环境感知联动四期修改；cce7a94 增加删除、停用任务时的提示；2026-09-09 动作链控制类动作后须紧跟延时、开关机锁定选项更名禁止关机/禁止启动</v>
+        <v>efb75df 环境感知联动四期修改；cce7a94 增加删除、停用任务时的提示；2026-09-09 动作链控制类动作后须紧跟延时、开关机锁定选项更名禁止关机/禁止启动；任务日志增加状态变动记录（创建/编辑/启停）</v>
       </c>
     </row>
     <row r="6">
@@ -8811,7 +8957,7 @@
         <v>用例总数</v>
       </c>
       <c r="B6">
-        <v>172</v>
+        <v>175</v>
       </c>
     </row>
     <row r="7">
@@ -8945,10 +9091,10 @@
         <v>任务生命周期</v>
       </c>
       <c r="B21">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C21" t="str">
-        <v>启停确认、编辑、复制、删除、日志、摘要、分页和刷新</v>
+        <v>启停确认、编辑、复制、删除、日志、摘要、分页、刷新和状态变动日志（创建/编辑/启停）</v>
       </c>
     </row>
     <row r="22">
@@ -8997,7 +9143,7 @@
         <v>关键规则</v>
       </c>
       <c r="B27" t="str">
-        <v>最多4类且不重复的触发条件；至少1个条件和1个动作；相邻动作类型不得相同；控制类动作（空调控制/锁定控制）后必须紧跟一个延时（最后一个动作除外）；最后一个动作不得为延时；制热不得与制冷或除湿同时锁定。生效日期和生效时间仅控制动作链启动，不中断已启动动作；停用或删除仍立即终止执行实例。人在状态/门窗状态/湿度条件要求所选每个房间均绑定对应传感器,任一房间未绑定则阻止保存并提示;温度条件不做绑定校验,房间无温湿度传感器时使用空调回风温度判定。</v>
+        <v>最多4类且不重复的触发条件；至少1个条件和1个动作；相邻动作类型不得相同；控制类动作（空调控制/锁定控制）后必须紧跟一个延时（最后一个动作除外）；最后一个动作不得为延时；制热不得与制冷或除湿同时锁定。生效日期和生效时间仅控制动作链启动，不中断已启动动作；停用或删除仍立即终止执行实例。人在状态/门窗状态/湿度条件要求所选每个房间均绑定对应传感器,任一房间未绑定则阻止保存并提示;温度条件不做绑定校验,房间无温湿度传感器时使用空调回风温度判定。日志除动作执行记录外，同时记录任务状态变动（创建/编辑/启用/停用），编辑记录仅列实际变更的配置维度。</v>
       </c>
     </row>
   </sheetData>

--- a/testcase/环境感知联动功能测试用例.xlsx
+++ b/testcase/环境感知联动功能测试用例.xlsx
@@ -5885,7 +5885,7 @@
         <v>1. 将动作类型切换为“锁定控制”</v>
       </c>
       <c r="K117" t="str">
-        <v>显示开关机锁定、模式多选、温度锁定配置；默认均为不锁定。</v>
+        <v>显示开关机锁定、模式多选、温度锁定勾选框；默认均为不锁定。</v>
       </c>
       <c r="L117" t="str">
         <v>待测试</v>
@@ -6216,7 +6216,7 @@
         <v>温度锁定=开启</v>
       </c>
       <c r="J124" t="str">
-        <v>1. 选择“锁定温度范围”</v>
+        <v>1. 勾选“温度锁定”</v>
       </c>
       <c r="K124" t="str">
         <v>显示双手柄滑动条，默认下限16℃、上限30℃。</v>
@@ -8821,7 +8821,7 @@
         <v>日志</v>
       </c>
       <c r="E178" t="str">
-        <v>编辑任务内容记录实际变更维度</v>
+        <v>编辑任务写入日志</v>
       </c>
       <c r="F178" t="str">
         <v>P0</v>
@@ -8841,7 +8841,7 @@
 3. 保存后打开日志</v>
       </c>
       <c r="K178" t="str">
-        <v>日志中新增“编辑任务内容（生效日期、执行动作）”记录；括号内仅列出实际发生变更的配置维度，以“、”连接；不带条件状态前缀，执行结果列留空。</v>
+        <v>日志中新增“编辑任务内容”记录（仅记录编辑动作，不罗列具体变更维度）；不带条件状态前缀，执行结果列留空。</v>
       </c>
       <c r="L178" t="str">
         <v>待测试</v>
@@ -8949,7 +8949,7 @@
         <v>近期核心提交</v>
       </c>
       <c r="B5" t="str">
-        <v>efb75df 环境感知联动四期修改；cce7a94 增加删除、停用任务时的提示；2026-09-09 动作链控制类动作后须紧跟延时、开关机锁定选项更名禁止关机/禁止启动；任务日志增加状态变动记录（创建/编辑/启停）</v>
+        <v>efb75df 环境感知联动四期修改；cce7a94 增加删除、停用任务时的提示；2026-09-09 动作链控制类动作后须紧跟延时、开关机锁定选项更名禁止关机/禁止启动；任务日志增加状态变动记录（创建/编辑/启停）；温度锁定改勾选框、编辑日志简化</v>
       </c>
     </row>
     <row r="6">
@@ -9143,7 +9143,7 @@
         <v>关键规则</v>
       </c>
       <c r="B27" t="str">
-        <v>最多4类且不重复的触发条件；至少1个条件和1个动作；相邻动作类型不得相同；控制类动作（空调控制/锁定控制）后必须紧跟一个延时（最后一个动作除外）；最后一个动作不得为延时；制热不得与制冷或除湿同时锁定。生效日期和生效时间仅控制动作链启动，不中断已启动动作；停用或删除仍立即终止执行实例。人在状态/门窗状态/湿度条件要求所选每个房间均绑定对应传感器,任一房间未绑定则阻止保存并提示;温度条件不做绑定校验,房间无温湿度传感器时使用空调回风温度判定。日志除动作执行记录外，同时记录任务状态变动（创建/编辑/启用/停用），编辑记录仅列实际变更的配置维度。</v>
+        <v>最多4类且不重复的触发条件；至少1个条件和1个动作；相邻动作类型不得相同；控制类动作（空调控制/锁定控制）后必须紧跟一个延时（最后一个动作除外）；最后一个动作不得为延时；制热不得与制冷或除湿同时锁定。生效日期和生效时间仅控制动作链启动，不中断已启动动作；停用或删除仍立即终止执行实例。人在状态/门窗状态/湿度条件要求所选每个房间均绑定对应传感器,任一房间未绑定则阻止保存并提示;温度条件不做绑定校验,房间无温湿度传感器时使用空调回风温度判定。日志除动作执行记录外，同时记录任务状态变动（创建/编辑/启用/停用），编辑仅记录“编辑任务内容”动作，不罗列变更维度。</v>
       </c>
     </row>
   </sheetData>

--- a/testcase/环境感知联动功能测试用例.xlsx
+++ b/testcase/环境感知联动功能测试用例.xlsx
@@ -4997,7 +4997,7 @@
         <v>温度边界</v>
       </c>
       <c r="E99" t="str">
-        <v>空调控制温度 30℃</v>
+        <v>空调控制温度 31℃</v>
       </c>
       <c r="F99" t="str">
         <v>P1</v>
@@ -5009,7 +5009,7 @@
         <v>打开集控计费平台并登录项目账号（须开启环境感知监测偏好设置），进入“节能策略 &gt; 环境感知联动”页面。点击“新建任务”，进入新建任务弹窗。</v>
       </c>
       <c r="I99" t="str">
-        <v>控制温度=30</v>
+        <v>控制温度=31</v>
       </c>
       <c r="J99" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 空调控制动作输入温度_x000d_
@@ -5064,7 +5064,7 @@
 2. 点击“确定”</v>
       </c>
       <c r="K100" t="str">
-        <v>提示“空调控制温度请输入 16~30℃ 的整数”，任务不保存。</v>
+        <v>提示“空调控制温度请输入 16~31℃ 的整数”，任务不保存。</v>
       </c>
       <c r="L100" t="str">
         <v>待测试</v>
@@ -5093,7 +5093,7 @@
         <v>温度边界</v>
       </c>
       <c r="E101" t="str">
-        <v>空调控制温度 31℃</v>
+        <v>空调控制温度 32℃</v>
       </c>
       <c r="F101" t="str">
         <v>P0</v>
@@ -5105,14 +5105,14 @@
         <v>打开集控计费平台并登录项目账号（须开启环境感知监测偏好设置），进入“节能策略 &gt; 环境感知联动”页面。点击“新建任务”，进入新建任务弹窗。</v>
       </c>
       <c r="I101" t="str">
-        <v>控制温度=31</v>
+        <v>控制温度=32</v>
       </c>
       <c r="J101" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 空调控制动作输入温度_x000d_
 2. 点击“确定”</v>
       </c>
       <c r="K101" t="str">
-        <v>提示“空调控制温度请输入 16~30℃ 的整数”，任务不保存。</v>
+        <v>提示“空调控制温度请输入 16~31℃ 的整数”，任务不保存。</v>
       </c>
       <c r="L101" t="str">
         <v>待测试</v>
@@ -5160,7 +5160,7 @@
 2. 点击“确定”</v>
       </c>
       <c r="K102" t="str">
-        <v>提示“空调控制温度请输入 16~30℃ 的整数”，任务不保存。</v>
+        <v>提示“空调控制温度请输入 16~31℃ 的整数”，任务不保存。</v>
       </c>
       <c r="L102" t="str">
         <v>待测试</v>
@@ -6219,7 +6219,7 @@
         <v>1. 勾选“温度锁定”</v>
       </c>
       <c r="K124" t="str">
-        <v>显示双手柄滑动条，默认下限16℃、上限30℃。</v>
+        <v>显示双手柄滑动条，默认下限16℃、上限31℃。</v>
       </c>
       <c r="L124" t="str">
         <v>待测试</v>
@@ -8949,7 +8949,7 @@
         <v>近期核心提交</v>
       </c>
       <c r="B5" t="str">
-        <v>efb75df 环境感知联动四期修改；cce7a94 增加删除、停用任务时的提示；2026-09-09 动作链控制类动作后须紧跟延时、开关机锁定选项更名禁止关机/禁止启动；任务日志增加状态变动记录（创建/编辑/启停）；温度锁定改勾选框、编辑日志简化</v>
+        <v>efb75df 环境感知联动四期修改；cce7a94 增加删除、停用任务时的提示；2026-09-09 动作链控制类动作后须紧跟延时、开关机锁定选项更名禁止关机/禁止启动；任务日志增加状态变动记录（创建/编辑/启停）；温度锁定改勾选框、编辑日志简化；空调控制/锁定温度范围更正为16~31℃</v>
       </c>
     </row>
     <row r="6">
@@ -9135,7 +9135,7 @@
         <v>关键边界</v>
       </c>
       <c r="B26" t="str">
-        <v>温度触发 -10~50℃；湿度 1~99%；持续 1~60分钟；延时 5~240分钟；空调温度 16~30℃；锁定温度 16~30℃；执行动作最多16个。</v>
+        <v>温度触发 -10~50℃；湿度 1~99%；持续 1~60分钟；延时 5~240分钟；空调温度 16~31℃；锁定温度 16~31℃；执行动作最多16个。</v>
       </c>
     </row>
     <row r="27">

--- a/testcase/环境感知联动功能测试用例.xlsx
+++ b/testcase/环境感知联动功能测试用例.xlsx
@@ -2127,7 +2127,7 @@
 3. 点击“确定”</v>
       </c>
       <c r="K39" t="str">
-        <v>提示“请选择房间/传感器”，任务不保存。</v>
+        <v>提示“请选择房间”，任务不保存。</v>
       </c>
       <c r="L39" t="str">
         <v>待测试</v>
@@ -8949,7 +8949,7 @@
         <v>近期核心提交</v>
       </c>
       <c r="B5" t="str">
-        <v>efb75df 环境感知联动四期修改；cce7a94 增加删除、停用任务时的提示；2026-09-09 动作链控制类动作后须紧跟延时、开关机锁定选项更名禁止关机/禁止启动；任务日志增加状态变动记录（创建/编辑/启停）；温度锁定改勾选框、编辑日志简化；空调控制/锁定温度范围更正为16~31℃</v>
+        <v>efb75df 环境感知联动四期修改；cce7a94 增加删除、停用任务时的提示；2026-09-09 动作链控制类动作后须紧跟延时、开关机锁定选项更名禁止关机/禁止启动；任务日志增加状态变动记录（创建/编辑/启停）；温度锁定改勾选框、编辑日志简化；空调控制/锁定温度范围更正为16~31℃；清除房间/传感器残留文案</v>
       </c>
     </row>
     <row r="6">
